--- a/StructureDefinition-ng-bundle-patient-to-insurer.xlsx
+++ b/StructureDefinition-ng-bundle-patient-to-insurer.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/StructureDefinition/ng-bundle-patient-to-insurer</t>
+    <t>https://www.dhin-hie.org/IGs/StructureDefinition/ng-bundle-patient-to-insurer</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-02T14:19:18+01:00</t>
+    <t>2025-09-10T08:54:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1016,7 +1016,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://dhin.org/2025Connectathon/StructureDefinition/NgPatient}
+    <t xml:space="preserve">Patient {https://www.dhin-hie.org/IGs/StructureDefinition/NgPatient}
 </t>
   </si>
   <si>
@@ -1131,7 +1131,7 @@
     <t>Bundle.entry:coverageEligibilityRequest.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">CoverageEligibilityRequest {https://dhin.org/2025Connectathon/StructureDefinition/ng-eligibility-request}
+    <t xml:space="preserve">CoverageEligibilityRequest {https://www.dhin-hie.org/IGs/StructureDefinition/ng-eligibility-request}
 </t>
   </si>
   <si>
@@ -1243,7 +1243,7 @@
     <t>Bundle.entry:coverage.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-coverage}
+    <t xml:space="preserve">Coverage {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-coverage}
 </t>
   </si>
   <si>
@@ -1358,7 +1358,7 @@
     <t>Bundle.entry:organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://dhin.org/2025Connectathon/StructureDefinition/ng-imm-organization}
+    <t xml:space="preserve">Organization {https://www.dhin-hie.org/IGs/StructureDefinition/ng-imm-organization}
 </t>
   </si>
   <si>
@@ -1473,7 +1473,7 @@
     <t>Bundle.entry:coverageEligibilityResponse.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">CoverageEligibilityResponse {https://dhin.org/2025Connectathon/StructureDefinition/ng-eligibility-response}
+    <t xml:space="preserve">CoverageEligibilityResponse {https://www.dhin-hie.org/IGs/StructureDefinition/ng-eligibility-response}
 </t>
   </si>
   <si>
@@ -1912,7 +1912,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.06640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.15234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
